--- a/data/trans_bre/P12_1_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P12_1_R-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 11,33</t>
+          <t>-0,84; 11,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,84; 26,73</t>
+          <t>10,64; 26,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,32; 16,07</t>
+          <t>0,86; 16,07</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 4,64</t>
+          <t>-1,34; 4,58</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 120,07</t>
+          <t>-6,83; 119,66</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,57; 136,03</t>
+          <t>37,78; 134,83</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,96; 78,74</t>
+          <t>2,03; 78,99</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-26,42; 228,41</t>
+          <t>-25,77; 197,96</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,93; 18,28</t>
+          <t>7,15; 17,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,49; 13,79</t>
+          <t>3,99; 13,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,52; 6,98</t>
+          <t>0,34; 6,92</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 8,6</t>
+          <t>-0,96; 8,5</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>26,75; 92,4</t>
+          <t>27,14; 93,31</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,43; 151,04</t>
+          <t>29,27; 152,88</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,83; 164,49</t>
+          <t>3,21; 178,8</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 93,66</t>
+          <t>-7,48; 90,35</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 6,89</t>
+          <t>-1,43; 7,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,89; 14,64</t>
+          <t>2,33; 14,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 8,91</t>
+          <t>-1,89; 8,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,01; 9,24</t>
+          <t>0,96; 9,41</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-22,23; 169,89</t>
+          <t>-21,4; 156,44</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,13; 137,96</t>
+          <t>11,81; 122,86</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-12,7; 86,46</t>
+          <t>-14,11; 88,89</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,92; 145,47</t>
+          <t>6,79; 139,61</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 10,69</t>
+          <t>0,14; 10,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,8; 23,88</t>
+          <t>12,07; 24,65</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,96; 15,83</t>
+          <t>2,79; 15,66</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-9,7; 4,42</t>
+          <t>-8,53; 5,49</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 100,05</t>
+          <t>0,69; 100,99</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>54,96; 162,43</t>
+          <t>57,91; 170,93</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,25; 107,35</t>
+          <t>14,32; 106,3</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-50,19; 36,02</t>
+          <t>-44,51; 46,26</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 16,11</t>
+          <t>-0,59; 16,64</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,06; 23,48</t>
+          <t>8,62; 23,42</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 11,83</t>
+          <t>-4,45; 11,65</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,44; 17,96</t>
+          <t>2,4; 17,29</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 79,9</t>
+          <t>-3,01; 82,02</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>58,46; 296,56</t>
+          <t>58,65; 305,18</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-17,21; 77,19</t>
+          <t>-19,6; 75,03</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,68; 54,43</t>
+          <t>5,54; 51,69</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 10,17</t>
+          <t>-0,67; 10,28</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,68; 15,77</t>
+          <t>2,12; 15,27</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,92; 14,7</t>
+          <t>2,82; 15,04</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 7,58</t>
+          <t>-2,71; 7,38</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-11,97; 135,36</t>
+          <t>-5,24; 155,29</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12,17; 143,33</t>
+          <t>11,27; 142,61</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12,19; 177,25</t>
+          <t>20,62; 190,61</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-15,4; 69,22</t>
+          <t>-17,42; 69,52</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,79; 9,77</t>
+          <t>1,48; 9,73</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,91; 10,75</t>
+          <t>1,98; 10,74</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 7,94</t>
+          <t>-0,64; 7,83</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7,94; 50,72</t>
+          <t>8,02; 55,27</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>12,78; 95,62</t>
+          <t>8,81; 98,3</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,93; 71,56</t>
+          <t>9,6; 72,31</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 70,83</t>
+          <t>-4,48; 67,6</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>42,91; 330,24</t>
+          <t>43,13; 383,32</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 5,66</t>
+          <t>-2,76; 6,41</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,75; 11,52</t>
+          <t>2,52; 11,46</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,37; 6,59</t>
+          <t>1,12; 6,39</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5,38; 14,95</t>
+          <t>6,0; 14,63</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-11,1; 23,27</t>
+          <t>-9,75; 26,25</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,62; 77,2</t>
+          <t>12,64; 79,55</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,27; 174,65</t>
+          <t>17,01; 156,38</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>50,93; 411,15</t>
+          <t>56,31; 359,89</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3,61; 7,31</t>
+          <t>3,65; 7,42</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>8,18; 12,07</t>
+          <t>8,3; 12,04</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3,45; 6,67</t>
+          <t>3,23; 6,68</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5,59; 25,63</t>
+          <t>5,45; 26,46</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>19,77; 45,95</t>
+          <t>20,35; 46,14</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>48,25; 80,52</t>
+          <t>48,74; 79,47</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>27,82; 62,09</t>
+          <t>25,75; 61,27</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>42,47; 225,35</t>
+          <t>40,26; 231,53</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P12_1_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P12_1_R-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,73</t>
+          <t>2,05</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>45,49%</t>
+          <t>59,69%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 11,4</t>
+          <t>-1,2; 11,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,64; 26,71</t>
+          <t>10,01; 25,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,86; 16,07</t>
+          <t>0,86; 15,87</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 4,58</t>
+          <t>-0,51; 4,62</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,83; 119,66</t>
+          <t>-9,74; 110,69</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>37,78; 134,83</t>
+          <t>36,47; 131,24</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,03; 78,99</t>
+          <t>3,01; 79,65</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-25,77; 197,96</t>
+          <t>-12,8; 221,06</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,96</t>
+          <t>3,92</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>31,64%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,15; 17,85</t>
+          <t>6,62; 17,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,99; 13,55</t>
+          <t>4,31; 13,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,34; 6,92</t>
+          <t>0,35; 6,71</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 8,5</t>
+          <t>-0,84; 8,41</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>27,14; 93,31</t>
+          <t>26,79; 89,14</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,27; 152,88</t>
+          <t>31,0; 152,65</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,21; 178,8</t>
+          <t>5,24; 168,44</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-7,48; 90,35</t>
+          <t>-5,97; 87,24</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5,16</t>
+          <t>5,35</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>57,77%</t>
+          <t>61,99%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 7,06</t>
+          <t>-1,65; 6,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,33; 14,36</t>
+          <t>2,18; 14,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 8,24</t>
+          <t>-1,48; 9,03</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,96; 9,41</t>
+          <t>1,08; 9,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-21,4; 156,44</t>
+          <t>-24,02; 148,15</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,81; 122,86</t>
+          <t>11,22; 126,89</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-14,11; 88,89</t>
+          <t>-11,4; 93,17</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,79; 139,61</t>
+          <t>10,51; 142,83</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-1,24</t>
+          <t>3,47</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-8,21%</t>
+          <t>24,79%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,14; 10,71</t>
+          <t>0,09; 10,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12,07; 24,65</t>
+          <t>11,05; 24,54</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,79; 15,66</t>
+          <t>2,96; 15,63</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-8,53; 5,49</t>
+          <t>-2,38; 8,75</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,69; 100,99</t>
+          <t>0,58; 100,69</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>57,91; 170,93</t>
+          <t>51,95; 167,67</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,32; 106,3</t>
+          <t>13,58; 103,92</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-44,51; 46,26</t>
+          <t>-13,59; 82,8</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10,29</t>
+          <t>10,6</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>28,43%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 16,64</t>
+          <t>-1,01; 17,14</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,62; 23,42</t>
+          <t>8,63; 22,87</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 11,65</t>
+          <t>-4,67; 10,9</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,4; 17,29</t>
+          <t>3,74; 18,37</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 82,02</t>
+          <t>-3,54; 84,85</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>58,65; 305,18</t>
+          <t>54,89; 289,73</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-19,6; 75,03</t>
+          <t>-19,4; 72,85</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,54; 51,69</t>
+          <t>8,41; 56,68</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2,36</t>
+          <t>2,59</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>20,43%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 10,28</t>
+          <t>-1,1; 9,61</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,12; 15,27</t>
+          <t>1,87; 15,41</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,82; 15,04</t>
+          <t>2,35; 14,87</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 7,38</t>
+          <t>-1,98; 7,38</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 155,29</t>
+          <t>-9,75; 126,91</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11,27; 142,61</t>
+          <t>10,56; 140,87</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>20,62; 190,61</t>
+          <t>16,26; 190,76</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-17,42; 69,52</t>
+          <t>-13,55; 72,89</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27,03</t>
+          <t>8,97</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>151,94%</t>
+          <t>50,67%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,48; 9,73</t>
+          <t>1,91; 9,43</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,98; 10,74</t>
+          <t>2,04; 10,78</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 7,83</t>
+          <t>-0,44; 7,72</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8,02; 55,27</t>
+          <t>4,47; 13,51</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>8,81; 98,3</t>
+          <t>12,4; 93,43</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,6; 72,31</t>
+          <t>10,68; 73,01</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,48; 67,6</t>
+          <t>-2,99; 67,16</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>43,13; 383,32</t>
+          <t>22,61; 94,41</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9,56</t>
+          <t>7,46</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>128,88%</t>
+          <t>76,78%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 6,41</t>
+          <t>-2,82; 5,95</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,52; 11,46</t>
+          <t>2,71; 11,22</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,12; 6,39</t>
+          <t>1,27; 6,5</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6,0; 14,63</t>
+          <t>4,35; 10,49</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-9,75; 26,25</t>
+          <t>-10,04; 25,11</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,64; 79,55</t>
+          <t>14,0; 79,25</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,01; 156,38</t>
+          <t>20,49; 169,64</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>56,31; 359,89</t>
+          <t>36,29; 125,27</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10,87</t>
+          <t>6,12</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>86,46%</t>
+          <t>45,77%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3,65; 7,42</t>
+          <t>3,38; 7,36</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>8,3; 12,04</t>
+          <t>8,25; 12,25</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3,23; 6,68</t>
+          <t>3,24; 6,78</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5,45; 26,46</t>
+          <t>4,48; 7,8</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>20,35; 46,14</t>
+          <t>19,08; 46,52</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>48,74; 79,47</t>
+          <t>49,0; 82,55</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>25,75; 61,27</t>
+          <t>25,82; 61,81</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>40,26; 231,53</t>
+          <t>31,34; 62,27</t>
         </is>
       </c>
     </row>
